--- a/survey_templates/033_dental_hygiene_quiz_how_well_do_you_brush--survey_templates.xlsx
+++ b/survey_templates/033_dental_hygiene_quiz_how_well_do_you_brush--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'18-24'}</t>
+          <t>18-24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': '18-24'}</t>
+          <t>18-24</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'25-34'}</t>
+          <t>25-34</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': '25-34'}</t>
+          <t>25-34</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'35-44'}</t>
+          <t>35-44</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': '35-44'}</t>
+          <t>35-44</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'45-54'}</t>
+          <t>45-54</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': '45-54'}</t>
+          <t>45-54</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'55_or_older'}</t>
+          <t>55_or_older</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': '55 or older'}</t>
+          <t>55 or older</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'morning_and_night'}</t>
+          <t>morning_and_night</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Morning and night'}</t>
+          <t>Morning and night</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'morning_only'}</t>
+          <t>morning_only</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Morning only'}</t>
+          <t>Morning only</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'none_of_the_above'}</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'None of the above'}</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'toothpaste'}</t>
+          <t>toothpaste</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Toothpaste'}</t>
+          <t>Toothpaste</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'mouthwash'}</t>
+          <t>mouthwash</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Mouthwash'}</t>
+          <t>Mouthwash</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'floss'}</t>
+          <t>floss</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Floss'}</t>
+          <t>Floss</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'none_of_the_above'}</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'None of the above'}</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'fresh_fruit'}</t>
+          <t>fresh_fruit</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Fresh fruit'}</t>
+          <t>Fresh fruit</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'vegetables'}</t>
+          <t>vegetables</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Vegetables'}</t>
+          <t>Vegetables</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'nuts'}</t>
+          <t>nuts</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Nuts'}</t>
+          <t>Nuts</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'none_of_the_above'}</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'None of the above'}</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'water'}</t>
+          <t>water</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Water'}</t>
+          <t>Water</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'low-sugar_drinks'}</t>
+          <t>low-sugar_drinks</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Low-sugar drinks'}</t>
+          <t>Low-sugar drinks</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'juice'}</t>
+          <t>juice</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Juice'}</t>
+          <t>Juice</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'none_of_the_above'}</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'None of the above'}</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'some_days'}</t>
+          <t>some_days</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Some days'}</t>
+          <t>Some days</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'every_day'}</t>
+          <t>every_day</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Every day'}</t>
+          <t>Every day</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'regular_check-ups_with_dentist'}</t>
+          <t>regular_check-ups_with_dentist</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Regular check-ups with dentist'}</t>
+          <t>Regular check-ups with dentist</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'irregular_check-ups_with_dentist'}</t>
+          <t>irregular_check-ups_with_dentist</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Irregular check-ups with dentist'}</t>
+          <t>Irregular check-ups with dentist</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'visit_dental_care_clinic_for_regular_check-ups'}</t>
+          <t>visit_dental_care_clinic_for_regular_check-ups</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Visit dental care clinic for regular check-ups'}</t>
+          <t>Visit dental care clinic for regular check-ups</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'visit_dental_care_clinic_for_emergencies'}</t>
+          <t>visit_dental_care_clinic_for_emergencies</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Visit dental care clinic for emergencies'}</t>
+          <t>Visit dental care clinic for emergencies</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'have_dental_insurance'}</t>
+          <t>have_dental_insurance</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Have dental insurance'}</t>
+          <t>Have dental insurance</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'do_not_have_dental_insurance'}</t>
+          <t>do_not_have_dental_insurance</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Do not have dental insurance'}</t>
+          <t>Do not have dental insurance</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'regularly'}</t>
+          <t>regularly</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Regularly'}</t>
+          <t>Regularly</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'irregularly'}</t>
+          <t>irregularly</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'Irregularly'}</t>
+          <t>Irregularly</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'very_well'}</t>
+          <t>very_well</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'Very well'}</t>
+          <t>Very well</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_well'}</t>
+          <t>somewhat_well</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat well'}</t>
+          <t>Somewhat well</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_'not_very_well'}</t>
+          <t>not_very_well</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 'Not very well'}</t>
+          <t>Not very well</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_'every_6_months'}</t>
+          <t>every_6_months</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': 'Every 6 months'}</t>
+          <t>Every 6 months</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_'every_year'}</t>
+          <t>every_year</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': 'Every year'}</t>
+          <t>Every year</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'label':_'less_often'}</t>
+          <t>less_often</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'label': 'Less often'}</t>
+          <t>Less often</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'label':_'every_day'}</t>
+          <t>every_day</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'label': 'Every day'}</t>
+          <t>Every day</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'label':_'every_week'}</t>
+          <t>every_week</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'label': 'Every week'}</t>
+          <t>Every week</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'label':_'every_month'}</t>
+          <t>every_month</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'label': 'Every month'}</t>
+          <t>Every month</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
